--- a/input/ES/alignment_targets_inSchool.xlsx
+++ b/input/ES/alignment_targets_inSchool.xlsx
@@ -85,7 +85,7 @@
     <t>Produced</t>
   </si>
   <si>
-    <t>11 Aug 2026</t>
+    <t>26 Sep 2026</t>
   </si>
 </sst>
 </file>
@@ -539,7 +539,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="14">
-        <v>0.37736731767654419</v>
+        <v>0.37736943364143372</v>
       </c>
     </row>
     <row r="3">
@@ -547,7 +547,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="15">
-        <v>0.39836278557777405</v>
+        <v>0.39836478233337402</v>
       </c>
     </row>
     <row r="4">
@@ -555,7 +555,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="16">
-        <v>0.42633265256881714</v>
+        <v>0.42633387446403503</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="17">
-        <v>0.44985359907150269</v>
+        <v>0.44985434412956238</v>
       </c>
     </row>
     <row r="6">
@@ -571,7 +571,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="18">
-        <v>0.43544408679008484</v>
+        <v>0.43544447422027588</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="19">
-        <v>0.44046884775161743</v>
+        <v>0.44047006964683533</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="20">
-        <v>0.40895813703536987</v>
+        <v>0.40895894169807434</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="21">
-        <v>0.42933732271194458</v>
+        <v>0.42933648824691772</v>
       </c>
     </row>
     <row r="10">
@@ -603,7 +603,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="22">
-        <v>0.41057506203651428</v>
+        <v>0.41057586669921875</v>
       </c>
     </row>
     <row r="11">
@@ -611,7 +611,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="23">
-        <v>0.41515487432479858</v>
+        <v>0.41516593098640442</v>
       </c>
     </row>
     <row r="12">
@@ -627,7 +627,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="25">
-        <v>0.55409532785415649</v>
+        <v>0.5540967583656311</v>
       </c>
     </row>
     <row r="14">
@@ -635,7 +635,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="26">
-        <v>0.54384309053421021</v>
+        <v>0.54384499788284302</v>
       </c>
     </row>
   </sheetData>
